--- a/排课结果/调课失败的排课失败课程_特殊放宽后.xlsx
+++ b/排课结果/调课失败的排课失败课程_特殊放宽后.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B177"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,1162 +1379,994 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>110000460.006</t>
+          <t>091000021.001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>高等数学b-2</t>
+          <t>网页设计基础</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>110000480.001</t>
+          <t>121000111.004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>社会主义发展史</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>110000480.002</t>
+          <t>121000121.001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>高等数学c-2</t>
+          <t>大学生职业软技能实训课程</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>110000670.002</t>
+          <t>14200002.006</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>高等数学a-2</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>091000021.001</t>
+          <t>14200002.009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>网页设计基础</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>121000111.004</t>
+          <t>14200002.075</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>社会主义发展史</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>121000121.001</t>
+          <t>14200002.076</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>大学生职业软技能实训课程</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>130000510.002</t>
+          <t>14200002.077</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>130000510.004</t>
+          <t>14200002.078</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>130000510.005</t>
+          <t>14200002.080</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>大学外语2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>130000510.006</t>
+          <t>171000121.032</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>影视鉴赏</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>130000510.007</t>
+          <t>261000011.001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>生活中的健康管理</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>130000510.008</t>
+          <t>26100003M.006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>“救”在你身边</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>130000510.009</t>
+          <t>61660003.001</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>音乐美学</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>130000510.010</t>
+          <t>61660003.002</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>大学物理（一）</t>
+          <t>音乐美学</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14200002.006</t>
+          <t>61660004.002</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐鉴赏</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>14200002.009</t>
+          <t>61660008.001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>世界音乐与多元文化</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14200002.075</t>
+          <t>61660009.001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>怀川弦歌：黄河文明的乐舞史诗</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14200002.076</t>
+          <t>61660010.002</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>舞蹈鉴赏</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14200002.077</t>
+          <t>61660011.001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14200002.078</t>
+          <t>61660011.002</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>戏剧鉴赏</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14200002.080</t>
+          <t>61660012.002</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>大学外语2</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15ALT016.003</t>
+          <t>61660012.004</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>队田径业余队</t>
+          <t>音乐的美感特征：流行中的音乐</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>171000121.032</t>
+          <t>61921003.001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>影视鉴赏</t>
+          <t>职场礼仪与高情商沟通</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>261000011.001</t>
+          <t>62221001.002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>生活中的健康管理</t>
+          <t>侦探之旅：从柯南道尔到AI司鉴</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>26100003M.006</t>
+          <t>081010790.001</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>“救”在你身边</t>
+          <t>高电压技术</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>61660003.001</t>
+          <t>081010810.001</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>现代电气控制技术与PLC</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>61660003.002</t>
+          <t>090010740.002</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>音乐美学</t>
+          <t>大数据分析技术</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>61660004.002</t>
+          <t>091010020.001</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>音乐鉴赏</t>
+          <t>算法分析与设计</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>61660008.001</t>
+          <t>091017031.001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>世界音乐与多元文化</t>
+          <t>文献检索与科技论文写作</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>61660009.001</t>
+          <t>091058011.001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>怀川弦歌：黄河文明的乐舞史诗</t>
+          <t>软件新技术讲座</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>61660010.002</t>
+          <t>150010280.001</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>舞蹈鉴赏</t>
+          <t>运动处方理论与应用</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>61660011.001</t>
+          <t>150130580.002</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>61660011.002</t>
+          <t>150130580.003</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>戏剧鉴赏</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>61660012.002</t>
+          <t>150130580.004</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>61660012.004</t>
+          <t>150130580.005</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>音乐的美感特征：流行中的音乐</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>61921003.001</t>
+          <t>150130580.006</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>职场礼仪与高情商沟通</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>62221001.002</t>
+          <t>150130580.007</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>侦探之旅：从柯南道尔到AI司鉴</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>081010790.001</t>
+          <t>150130580.008</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>高电压技术</t>
+          <t>专项4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>081010810.001</t>
+          <t>150130680.002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>现代电气控制技术与PLC</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>090010740.002</t>
+          <t>150130680.003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>大数据分析技术</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>091010020.001</t>
+          <t>150130680.004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>算法分析与设计</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>091017031.001</t>
+          <t>150130680.005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>文献检索与科技论文写作</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>091058011.001</t>
+          <t>150130680.006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>软件新技术讲座</t>
+          <t>专项2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>110010321.001</t>
+          <t>150130700.001</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>高等代数2</t>
+          <t>私人教练指导</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>150010280.001</t>
+          <t>150130880.001</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>运动处方理论与应用</t>
+          <t>健身俱乐部经营与管理</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>150130580.002</t>
+          <t>150140220.001</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>民间武术套路2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>150130580.003</t>
+          <t>150140470.002</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>150130580.004</t>
+          <t>150140470.003</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>150130580.005</t>
+          <t>150140470.004</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>150130580.006</t>
+          <t>150140490.002</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>150130580.007</t>
+          <t>150140490.003</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>150130580.008</t>
+          <t>150140490.004</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>专项4</t>
+          <t>武术竞赛与训练4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>150130680.002</t>
+          <t>150140570.001</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>散打2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>150130680.003</t>
+          <t>150140670.002</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>150130680.004</t>
+          <t>150140670.003</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>150130680.005</t>
+          <t>150140670.004</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>150130680.006</t>
+          <t>150140760.002</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>专项2</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>150130700.001</t>
+          <t>150140760.003</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>私人教练指导</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>150130880.001</t>
+          <t>150140760.004</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>健身俱乐部经营与管理</t>
+          <t>专项5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>150140220.001</t>
+          <t>151130120.001</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>民间武术套路2</t>
+          <t>乒乓球</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>150140470.002</t>
+          <t>160060320.047</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>150140470.003</t>
+          <t>160060320.048</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>150140470.004</t>
+          <t>160060320.049</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>武术竞赛与训练2</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>150140490.002</t>
+          <t>160060320.050</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>150140490.003</t>
+          <t>160060320.051</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>150140490.004</t>
+          <t>160060320.052</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>武术竞赛与训练4</t>
+          <t>声乐4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>150140570.001</t>
+          <t>160060340.047</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>散打2</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>150140670.002</t>
+          <t>160060340.048</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>150140670.003</t>
+          <t>160060340.049</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>150140670.004</t>
+          <t>160060340.050</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>专项3</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>150140760.002</t>
+          <t>160060340.051</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>150140760.003</t>
+          <t>160060360.040</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>150140760.004</t>
+          <t>160060360.041</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>专项5</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>151130120.001</t>
+          <t>160060360.042</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>乒乓球</t>
+          <t>声乐8</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>160060320.047</t>
+          <t>160060430.001</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐艺术史及作品欣赏2</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>160060320.048</t>
+          <t>16502002.041</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>160060320.049</t>
+          <t>16502002.042</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>160060320.050</t>
+          <t>16502002.043</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>160060320.051</t>
+          <t>16502002.044</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>声乐2</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>160060320.052</t>
+          <t>271010080.001</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>声乐4</t>
+          <t>Java EE开发技术</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>160060340.047</t>
+          <t>271010091.002</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>声乐6</t>
+          <t>移动开发技术</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>160060340.048</t>
+          <t>271030050.001</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>160060340.049</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>160060340.050</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>160060340.051</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>声乐6</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>160060360.040</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>160060360.041</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>160060360.042</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>声乐8</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>160060430.001</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>声乐艺术史及作品欣赏2</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>16502002.041</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>16502002.042</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>16502002.043</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>16502002.044</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>声乐2</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>271010080.001</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Java EE开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>271010091.002</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>移动开发技术</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>271030050.001</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
         <is>
           <t>网络编程提高</t>
         </is>
